--- a/laboratory_measurement_L-Com/results/measurement_data_processed.xlsx
+++ b/laboratory_measurement_L-Com/results/measurement_data_processed.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'measurement_data'!$A$1:$AO$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'measurement_data'!$A$1:$AO$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$O$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO28"/>
+  <dimension ref="A1:AO73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -473,7 +473,7 @@
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
@@ -829,13 +829,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>40931.01039881945</v>
+        <v>40931.01005048611</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.5016</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -871,40 +871,40 @@
         <v>100</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>997.0598</v>
+        <v>997.0608999999999</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.001170192</v>
+        <v>0.001130288</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.004638672</v>
+        <v>0.005249023</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>1495.749</v>
+        <v>1495.739</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.01044954</v>
+        <v>0.01202353</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.04321289</v>
+        <v>0.0447998</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>24.64495</v>
+        <v>24.64088</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.003775247</v>
+        <v>0.004382846</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>1496.22</v>
+        <v>1496.219</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.0005380613</v>
+        <v>0.0006385954</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>7.021479</v>
+        <v>7.021508</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>2.872056e-05</v>
+        <v>3.291966e-05</v>
       </c>
       <c r="AC3" s="2" t="n">
         <v>100</v>
@@ -938,7 +938,7 @@
       <c r="AN3" s="2" t="inlineStr"/>
       <c r="AO3" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
@@ -950,13 +950,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40931.01049619213</v>
+        <v>40931.01039881945</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.6418166666666667</v>
+        <v>0.5016</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -992,40 +992,40 @@
         <v>100</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>997.0596</v>
+        <v>997.0598</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.001176809</v>
+        <v>0.001170192</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>0.004638672</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>1495.752</v>
+        <v>1495.749</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.01034916</v>
+        <v>0.01044954</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.04284668</v>
+        <v>0.04321289</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>24.64603</v>
+        <v>24.64495</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.003716595</v>
+        <v>0.003775247</v>
       </c>
       <c r="Y4" s="2" t="n">
         <v>1496.22</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.0005300458</v>
+        <v>0.0005380613</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>7.02147</v>
+        <v>7.021479</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>2.840971e-05</v>
+        <v>2.872056e-05</v>
       </c>
       <c r="AC4" s="2" t="n">
         <v>100</v>
@@ -1068,22 +1068,22 @@
         <v>0</v>
       </c>
       <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="D5" s="3" t="n">
-        <v>46254.38756987268</v>
+        <v>40931.01039881945</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7665663.627916667</v>
+        <v>0.5016</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>100.36</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1006.87</v>
+        <v>100</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
@@ -1095,58 +1095,58 @@
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1107.23</v>
+        <v>100</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1.812812152849905</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3.62562430569981</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.62562430569981</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>90.93593923575048</v>
+        <v>100</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1004.935</v>
+        <v>997.0598</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.0006024943</v>
+        <v>0.001170192</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.003051758</v>
+        <v>0.004638672</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>1543.003</v>
+        <v>1495.749</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009023428999999999</v>
+        <v>0.01044954</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.04394531</v>
+        <v>0.04321289</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>23.70149</v>
+        <v>24.64495</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.003078766</v>
+        <v>0.003775247</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1497.912</v>
+        <v>1496.22</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.0008050053</v>
+        <v>0.0005380613</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>6.891023</v>
+        <v>7.021479</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>2.394567e-05</v>
+        <v>2.872056e-05</v>
       </c>
       <c r="AC5" s="2" t="n">
         <v>100</v>
@@ -1171,20 +1171,16 @@
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
       <c r="AK5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL5" s="2" t="inlineStr">
-        <is>
-          <t>+100.4 g SL120, +906.9 g Water</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="AN5" s="2" t="inlineStr"/>
       <c r="AO5" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
@@ -1193,22 +1189,22 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46254.3916984838</v>
+        <v>40931.01049619213</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7665669.573116667</v>
+        <v>0.6418166666666667</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>100.36</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1006.87</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
@@ -1220,58 +1216,58 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1107.23</v>
+        <v>100</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1.812812152849905</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3.62562430569981</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3.62562430569981</v>
+        <v>0</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>90.93593923575048</v>
+        <v>100</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1004.939</v>
+        <v>997.0596</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.0007044451</v>
+        <v>0.001176809</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.002929688</v>
+        <v>0.004638672</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>1542.997</v>
+        <v>1495.752</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.007206327</v>
+        <v>0.01034916</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.04016113</v>
+        <v>0.04284668</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>23.73992</v>
+        <v>24.64603</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.00429098</v>
+        <v>0.003716595</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>1497.922</v>
+        <v>1496.22</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.0009035594</v>
+        <v>0.0005300458</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>6.891049</v>
+        <v>7.02147</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.927731e-05</v>
+        <v>2.840971e-05</v>
       </c>
       <c r="AC6" s="2" t="n">
         <v>100</v>
@@ -1314,22 +1310,22 @@
         <v>0</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46254.39313792824</v>
+        <v>40931.01049619213</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7665671.645916668</v>
+        <v>0.6418166666666667</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>100.36</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1006.87</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
@@ -1341,58 +1337,58 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1107.23</v>
+        <v>100</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1.812812152849905</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3.62562430569981</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3.62562430569981</v>
+        <v>0</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>90.93593923575048</v>
+        <v>100</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>1004.94</v>
+        <v>997.0596</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.000712341</v>
+        <v>0.001176809</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.003051758</v>
+        <v>0.004638672</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>1542.991</v>
+        <v>1495.752</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.007771788</v>
+        <v>0.01034916</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.03881836</v>
+        <v>0.04284668</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>23.75398</v>
+        <v>24.64603</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.003282262</v>
+        <v>0.003716595</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>1497.925</v>
+        <v>1496.22</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.0008760545</v>
+        <v>0.0005300458</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>6.891068</v>
+        <v>7.02147</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>2.086574e-05</v>
+        <v>2.840971e-05</v>
       </c>
       <c r="AC7" s="2" t="n">
         <v>100</v>
@@ -1426,25 +1422,25 @@
       <c r="AN7" s="2" t="inlineStr"/>
       <c r="AO7" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46254.48084003472</v>
+        <v>46254.38756987268</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>7665663.627916667</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>100.36</v>
@@ -1480,40 +1476,40 @@
         <v>90.93593923575048</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>1005.29</v>
+        <v>1004.935</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.001352826</v>
+        <v>0.0006024943</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0.004943848</v>
+        <v>0.003051758</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>1541.424</v>
+        <v>1543.003</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.01041913</v>
+        <v>0.009023428999999999</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.04553223</v>
+        <v>0.04394531</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>23.72909</v>
+        <v>23.70149</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.001413905</v>
+        <v>0.003078766</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>1498.006</v>
+        <v>1497.912</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.0004556416</v>
+        <v>0.0008050053</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>6.895253</v>
+        <v>6.891023</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>2.809287e-05</v>
+        <v>2.394567e-05</v>
       </c>
       <c r="AC8" s="2" t="n">
         <v>100</v>
@@ -1538,9 +1534,13 @@
       </c>
       <c r="AJ8" s="2" t="inlineStr"/>
       <c r="AK8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AL8" s="2" t="inlineStr">
+        <is>
+          <t>+100.4 g SL120, +906.9 g Water</t>
+        </is>
+      </c>
       <c r="AM8" s="2" t="b">
         <v>1</v>
       </c>
@@ -1553,19 +1553,19 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46254.48753407408</v>
+        <v>46254.38756987268</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>9.639416666666667</v>
+        <v>7665663.627916667</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>100.36</v>
@@ -1601,52 +1601,52 @@
         <v>90.93593923575048</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>1005.355</v>
+        <v>1004.935</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.004100476</v>
+        <v>0.0006024943</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0.01470947</v>
+        <v>0.003051758</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>1541.047</v>
+        <v>1543.003</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.0244965</v>
+        <v>0.009023428999999999</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.09643554999999999</v>
+        <v>0.04394531</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>23.61622</v>
+        <v>23.70149</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.008507211000000001</v>
+        <v>0.003078766</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>1497.996</v>
+        <v>1497.912</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.0008300083</v>
+        <v>0.0008050053</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>6.896232</v>
+        <v>6.891023</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>6.335228000000001e-05</v>
+        <v>2.394567e-05</v>
       </c>
       <c r="AC9" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" s="2" t="n">
         <v>100</v>
@@ -1668,25 +1668,25 @@
       <c r="AN9" s="2" t="inlineStr"/>
       <c r="AO9" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46254.49456743056</v>
+        <v>46254.3916984838</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>19.76745</v>
+        <v>7665669.573116667</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>100.36</v>
@@ -1722,52 +1722,52 @@
         <v>90.93593923575048</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>1005.407</v>
+        <v>1004.939</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.004100963</v>
+        <v>0.0007044451</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>0.0144043</v>
+        <v>0.002929688</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>1540.782</v>
+        <v>1542.997</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.02505425</v>
+        <v>0.007206327</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.09265137</v>
+        <v>0.04016113</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>23.54464</v>
+        <v>23.73992</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.008219684</v>
+        <v>0.00429098</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>1497.994</v>
+        <v>1497.922</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.0008296818</v>
+        <v>0.0009035594</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>6.896921</v>
+        <v>6.891049</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>6.495976e-05</v>
+        <v>1.927731e-05</v>
       </c>
       <c r="AC10" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" s="2" t="n">
         <v>100</v>
@@ -1795,19 +1795,19 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46254.49474021991</v>
+        <v>46254.3916984838</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>20.01626666666667</v>
+        <v>7665669.573116667</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>100.36</v>
@@ -1843,52 +1843,52 @@
         <v>90.93593923575048</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>0</v>
+        <v>1004.939</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>0</v>
+        <v>0.0007044451</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>0</v>
+        <v>0.002929688</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0</v>
+        <v>1542.997</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>0</v>
+        <v>0.007206327</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>0</v>
+        <v>0.04016113</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0</v>
+        <v>23.73992</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>0</v>
+        <v>0.00429098</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>0</v>
+        <v>1497.922</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>0</v>
+        <v>0.0009035594</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>0</v>
+        <v>6.891049</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>0</v>
+        <v>1.927731e-05</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" s="2" t="n">
         <v>100</v>
@@ -1905,34 +1905,30 @@
       </c>
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="2" t="inlineStr">
-        <is>
-          <t>N &lt; 1; Rho_M outside 500.0..2000.0; C_M outside 1000.0..2200.0</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AN11" s="2" t="inlineStr"/>
       <c r="AO11" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46254.49612913194</v>
+        <v>46254.39313792824</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>22.0163</v>
+        <v>7665671.645916668</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>100.36</v>
@@ -1968,52 +1964,52 @@
         <v>90.93593923575048</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>1005.423</v>
+        <v>1004.94</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>0.003187256</v>
+        <v>0.000712341</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>0.01092529</v>
+        <v>0.003051758</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>1540.691</v>
+        <v>1542.991</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>0.01515166</v>
+        <v>0.007771788</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0.06555176</v>
+        <v>0.03881836</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>23.51149</v>
+        <v>23.75398</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>0.005927483</v>
+        <v>0.003282262</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>1497.991</v>
+        <v>1497.925</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>0.0003783404</v>
+        <v>0.0008760545</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>6.897154</v>
+        <v>6.891068</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>3.918599e-05</v>
+        <v>2.086574e-05</v>
       </c>
       <c r="AC12" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" s="2" t="n">
         <v>100</v>
@@ -2041,19 +2037,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46254.49751804398</v>
+        <v>46254.39313792824</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24.01633333333333</v>
+        <v>7665671.645916668</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>100.36</v>
@@ -2089,52 +2085,52 @@
         <v>90.93593923575048</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>1005.436</v>
+        <v>1004.94</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>0.003810688</v>
+        <v>0.000712341</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>0.01293945</v>
+        <v>0.003051758</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>1540.62</v>
+        <v>1542.991</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>0.02488237</v>
+        <v>0.007771788</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>0.1016846</v>
+        <v>0.03881836</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>23.48755</v>
+        <v>23.75398</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>0.008073735</v>
+        <v>0.003282262</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>1497.989</v>
+        <v>1497.925</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>0.001009231</v>
+        <v>0.0008760545</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>6.897338</v>
+        <v>6.891068</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>6.460313e-05</v>
+        <v>2.086574e-05</v>
       </c>
       <c r="AC13" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AD13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AF13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" s="2" t="n">
         <v>100</v>
@@ -2156,7 +2152,7 @@
       <c r="AN13" s="2" t="inlineStr"/>
       <c r="AO13" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
@@ -2165,16 +2161,16 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46254.50426260417</v>
+        <v>46254.48084003472</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>33.7285</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>100.36</v>
@@ -2183,7 +2179,7 @@
         <v>1006.87</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
@@ -2192,70 +2188,70 @@
         <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>999.0445999999999</v>
+        <v>1005.29</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>0.03992499</v>
+        <v>0.001352826</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>0.1965332</v>
+        <v>0.004943848</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>1572.356</v>
+        <v>1541.424</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>0.1521285</v>
+        <v>0.01041913</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>0.6082764000000001</v>
+        <v>0.04553223</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>24.34576</v>
+        <v>23.72909</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>0.0293769</v>
+        <v>0.001413905</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>1496.648</v>
+        <v>1498.006</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>0.01245824</v>
+        <v>0.0004556416</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>6.814262</v>
+        <v>6.895253</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>0.0003936504</v>
+        <v>2.809287e-05</v>
       </c>
       <c r="AC14" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AD14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" s="2" t="n">
         <v>100</v>
@@ -2268,13 +2264,9 @@
       </c>
       <c r="AJ14" s="2" t="inlineStr"/>
       <c r="AK14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL14" s="2" t="inlineStr">
-        <is>
-          <t>+40.1 g IPA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="b">
         <v>1</v>
       </c>
@@ -2290,16 +2282,16 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46254.50565151621</v>
+        <v>46254.48084003472</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>35.72853333333333</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>100.36</v>
@@ -2308,7 +2300,7 @@
         <v>1006.87</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>0</v>
@@ -2317,70 +2309,70 @@
         <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>999.0505000000001</v>
+        <v>1005.29</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>0.04014613</v>
+        <v>0.001352826</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>0.1531982</v>
+        <v>0.004943848</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>1571.906</v>
+        <v>1541.424</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>0.1086098</v>
+        <v>0.01041913</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>0.4274902</v>
+        <v>0.04553223</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>24.34135</v>
+        <v>23.72909</v>
       </c>
       <c r="X15" s="2" t="n">
-        <v>0.01313539</v>
+        <v>0.001413905</v>
       </c>
       <c r="Y15" s="2" t="n">
-        <v>1496.635</v>
+        <v>1498.006</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>0.009172156000000001</v>
+        <v>0.0004556416</v>
       </c>
       <c r="AA15" s="2" t="n">
-        <v>6.815417</v>
+        <v>6.895253</v>
       </c>
       <c r="AB15" s="2" t="n">
-        <v>0.0002764152</v>
+        <v>2.809287e-05</v>
       </c>
       <c r="AC15" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AD15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AF15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" s="2" t="n">
         <v>100</v>
@@ -2402,7 +2394,7 @@
       <c r="AN15" s="2" t="inlineStr"/>
       <c r="AO15" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
@@ -2411,16 +2403,16 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="D16" s="3" t="n">
-        <v>46254.50704042824</v>
+        <v>46254.48753407408</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>37.72856666666667</v>
+        <v>9.639416666666667</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>100.36</v>
@@ -2429,7 +2421,7 @@
         <v>1006.87</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>0</v>
@@ -2438,58 +2430,58 @@
         <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>999.053</v>
+        <v>1005.355</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>0.08086706</v>
+        <v>0.004100476</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>0.3322754</v>
+        <v>0.01470947</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>1571.665</v>
+        <v>1541.047</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>0.1730756</v>
+        <v>0.0244965</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>1.010498</v>
+        <v>0.09643554999999999</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>24.29788</v>
+        <v>23.61622</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>0.008551191</v>
+        <v>0.008507211000000001</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>1496.625</v>
+        <v>1497.996</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>0.01765049</v>
+        <v>0.0008300083</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>6.816027</v>
+        <v>6.896232</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>0.000443982</v>
+        <v>6.335228000000001e-05</v>
       </c>
       <c r="AC16" s="2" t="n">
         <v>100</v>
@@ -2532,16 +2524,16 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="D17" s="3" t="n">
-        <v>46254.50842932871</v>
+        <v>46254.48753407408</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>39.72858333333333</v>
+        <v>9.639416666666667</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>100.36</v>
@@ -2550,7 +2542,7 @@
         <v>1006.87</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>0</v>
@@ -2559,58 +2551,58 @@
         <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>999.2921</v>
+        <v>1005.355</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>0.06010251</v>
+        <v>0.004100476</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>0.2545776</v>
+        <v>0.01470947</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>1571.253</v>
+        <v>1541.047</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>0.08578891</v>
+        <v>0.0244965</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>0.3741455</v>
+        <v>0.09643554999999999</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>24.24398</v>
+        <v>23.61622</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>0.0163429</v>
+        <v>0.008507211000000001</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>1496.669</v>
+        <v>1497.996</v>
       </c>
       <c r="Z17" s="2" t="n">
-        <v>0.01277461</v>
+        <v>0.0008300083</v>
       </c>
       <c r="AA17" s="2" t="n">
-        <v>6.817075</v>
+        <v>6.896232</v>
       </c>
       <c r="AB17" s="2" t="n">
-        <v>0.0002167475</v>
+        <v>6.335228000000001e-05</v>
       </c>
       <c r="AC17" s="2" t="n">
         <v>100</v>
@@ -2644,7 +2636,7 @@
       <c r="AN17" s="2" t="inlineStr"/>
       <c r="AO17" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
@@ -2653,16 +2645,16 @@
         <v>1</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46254.50981824074</v>
+        <v>46254.49456743056</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>41.72861666666667</v>
+        <v>19.76745</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>100.36</v>
@@ -2671,7 +2663,7 @@
         <v>1006.87</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>0</v>
@@ -2680,58 +2672,58 @@
         <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>999.4417</v>
+        <v>1005.407</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>0.0439833</v>
+        <v>0.004100963</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>0.2298584</v>
+        <v>0.0144043</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>1570.984</v>
+        <v>1540.782</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>0.06117566</v>
+        <v>0.02505425</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>0.2178955</v>
+        <v>0.09265137</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>24.16846</v>
+        <v>23.54464</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>0.0183495</v>
+        <v>0.008219684</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>1496.688</v>
+        <v>1497.994</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>0.01092934</v>
+        <v>0.0008296818</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>6.817746</v>
+        <v>6.896921</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>0.0001529526</v>
+        <v>6.495976e-05</v>
       </c>
       <c r="AC18" s="2" t="n">
         <v>100</v>
@@ -2774,16 +2766,16 @@
         <v>1</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46254.51120715278</v>
+        <v>46254.49456743056</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>43.72865</v>
+        <v>19.76745</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>100.36</v>
@@ -2792,7 +2784,7 @@
         <v>1006.87</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>0</v>
@@ -2801,58 +2793,58 @@
         <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>999.497</v>
+        <v>1005.407</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>0.0747264</v>
+        <v>0.004100963</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>0.3393555</v>
+        <v>0.0144043</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>1570.849</v>
+        <v>1540.782</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>0.03224536</v>
+        <v>0.02505425</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>0.1621094</v>
+        <v>0.09265137</v>
       </c>
       <c r="W19" s="2" t="n">
-        <v>24.1036</v>
+        <v>23.54464</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>0.01423024</v>
+        <v>0.008219684</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>1496.687</v>
+        <v>1497.994</v>
       </c>
       <c r="Z19" s="2" t="n">
-        <v>0.01634002</v>
+        <v>0.0008296818</v>
       </c>
       <c r="AA19" s="2" t="n">
-        <v>6.818077</v>
+        <v>6.896921</v>
       </c>
       <c r="AB19" s="2" t="n">
-        <v>7.983372e-05</v>
+        <v>6.495976e-05</v>
       </c>
       <c r="AC19" s="2" t="n">
         <v>100</v>
@@ -2886,7 +2878,7 @@
       <c r="AN19" s="2" t="inlineStr"/>
       <c r="AO19" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
@@ -2895,16 +2887,16 @@
         <v>1</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>46254.51259606481</v>
+        <v>46254.49474021991</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45.72868333333334</v>
+        <v>20.01626666666667</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>100.36</v>
@@ -2913,7 +2905,7 @@
         <v>1006.87</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>0</v>
@@ -2922,61 +2914,61 @@
         <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>999.5633</v>
+        <v>0</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>0.01306258</v>
+        <v>0</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>0.04284668</v>
+        <v>0</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>1570.704</v>
+        <v>0</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>0.0494593</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>0.2075195</v>
+        <v>0</v>
       </c>
       <c r="W20" s="2" t="n">
-        <v>24.03886</v>
+        <v>0</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>0.0207684</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>1496.689</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>0.00212438</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>6.818432</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>0.0001221448</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="2" t="n">
         <v>0</v>
@@ -3002,9 +2994,13 @@
       </c>
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN20" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="2" t="inlineStr">
+        <is>
+          <t>N &lt; 1; Rho_M outside 500.0..2000.0; C_M outside 1000.0..2200.0</t>
+        </is>
+      </c>
       <c r="AO20" s="2" t="inlineStr">
         <is>
           <t>Kennfeld_v2 (6).csv</t>
@@ -3016,16 +3012,16 @@
         <v>1</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46254.51398497685</v>
+        <v>46254.49474021991</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>47.72871666666666</v>
+        <v>20.01626666666667</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>100.36</v>
@@ -3034,7 +3030,7 @@
         <v>1006.87</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>0</v>
@@ -3043,61 +3039,61 @@
         <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>999.6129</v>
+        <v>0</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>0.009706391</v>
+        <v>0</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>0.03479004</v>
+        <v>0</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>1570.538</v>
+        <v>0</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>0.03119711</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>0.130127</v>
+        <v>0</v>
       </c>
       <c r="W21" s="2" t="n">
-        <v>23.94936</v>
+        <v>0</v>
       </c>
       <c r="X21" s="2" t="n">
-        <v>0.01781276</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="2" t="n">
-        <v>1496.681</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>0.0009501228</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="2" t="n">
-        <v>6.818836</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="2" t="n">
-        <v>7.606435999999999e-05</v>
+        <v>0</v>
       </c>
       <c r="AC21" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="2" t="n">
         <v>0</v>
@@ -3123,12 +3119,16 @@
       </c>
       <c r="AL21" s="2" t="inlineStr"/>
       <c r="AM21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN21" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AN21" s="2" t="inlineStr">
+        <is>
+          <t>N &lt; 1; Rho_M outside 500.0..2000.0; C_M outside 1000.0..2200.0</t>
+        </is>
+      </c>
       <c r="AO21" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
@@ -3137,16 +3137,16 @@
         <v>1</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46254.51537388889</v>
+        <v>46254.49612913194</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>49.72875000000001</v>
+        <v>22.0163</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>100.36</v>
@@ -3155,7 +3155,7 @@
         <v>1006.87</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>0</v>
@@ -3164,58 +3164,58 @@
         <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>999.6426</v>
+        <v>1005.423</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>0.007244701</v>
+        <v>0.003187256</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>0.02783203</v>
+        <v>0.01092529</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>1570.443</v>
+        <v>1540.691</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>0.02649933</v>
+        <v>0.01515166</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>0.09753418</v>
+        <v>0.06555176</v>
       </c>
       <c r="W22" s="2" t="n">
-        <v>23.89672</v>
+        <v>23.51149</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>0.01020618</v>
+        <v>0.005927483</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>1496.679</v>
+        <v>1497.991</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0.000754301</v>
+        <v>0.0003783404</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>6.819066</v>
+        <v>6.897154</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>6.589015e-05</v>
+        <v>3.918599e-05</v>
       </c>
       <c r="AC22" s="2" t="n">
         <v>100</v>
@@ -3258,16 +3258,16 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46254.51676280093</v>
+        <v>46254.49612913194</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>51.72878333333334</v>
+        <v>22.0163</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>100.36</v>
@@ -3276,7 +3276,7 @@
         <v>1006.87</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0</v>
@@ -3285,58 +3285,58 @@
         <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>999.6674</v>
+        <v>1005.423</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>0.007222514</v>
+        <v>0.003187256</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>0.02850342</v>
+        <v>0.01092529</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>1570.347</v>
+        <v>1540.691</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>0.03095584</v>
+        <v>0.01515166</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>0.1275635</v>
+        <v>0.06555176</v>
       </c>
       <c r="W23" s="2" t="n">
-        <v>23.85612</v>
+        <v>23.51149</v>
       </c>
       <c r="X23" s="2" t="n">
-        <v>0.01159485</v>
+        <v>0.005927483</v>
       </c>
       <c r="Y23" s="2" t="n">
-        <v>1496.677</v>
+        <v>1497.991</v>
       </c>
       <c r="Z23" s="2" t="n">
-        <v>0.001201592</v>
+        <v>0.0003783404</v>
       </c>
       <c r="AA23" s="2" t="n">
-        <v>6.819304</v>
+        <v>6.897154</v>
       </c>
       <c r="AB23" s="2" t="n">
-        <v>7.697795e-05</v>
+        <v>3.918599e-05</v>
       </c>
       <c r="AC23" s="2" t="n">
         <v>100</v>
@@ -3370,7 +3370,7 @@
       <c r="AN23" s="2" t="inlineStr"/>
       <c r="AO23" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
@@ -3379,16 +3379,16 @@
         <v>1</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46254.51815171296</v>
+        <v>46254.49751804398</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>53.72881666666667</v>
+        <v>24.01633333333333</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>100.36</v>
@@ -3397,7 +3397,7 @@
         <v>1006.87</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
@@ -3406,58 +3406,58 @@
         <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>999.6983</v>
+        <v>1005.436</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>0.007676615</v>
+        <v>0.003810688</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>0.03082275</v>
+        <v>0.01293945</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>1570.217</v>
+        <v>1540.62</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>0.03773323</v>
+        <v>0.02488237</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>0.1420898</v>
+        <v>0.1016846</v>
       </c>
       <c r="W24" s="2" t="n">
-        <v>23.80157</v>
+        <v>23.48755</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>0.01671878</v>
+        <v>0.008073735</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>1496.672</v>
+        <v>1497.989</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>0.002357753</v>
+        <v>0.001009231</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>6.819623</v>
+        <v>6.897338</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>9.30431e-05</v>
+        <v>6.460313e-05</v>
       </c>
       <c r="AC24" s="2" t="n">
         <v>100</v>
@@ -3500,16 +3500,16 @@
         <v>1</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46254.519540625</v>
+        <v>46254.49751804398</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>55.72885</v>
+        <v>24.01633333333333</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>100.36</v>
@@ -3518,7 +3518,7 @@
         <v>1006.87</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>40.15</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>0</v>
@@ -3527,58 +3527,58 @@
         <v>0</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1147.38</v>
+        <v>1107.23</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1.749376841151144</v>
+        <v>1.812812152849905</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6.998030295107114</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>3.498753682302289</v>
+        <v>3.62562430569981</v>
       </c>
       <c r="O25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>87.75383918143945</v>
+        <v>90.93593923575048</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>999.7319</v>
+        <v>1005.436</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>0.009771835</v>
+        <v>0.003810688</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>0.03417969</v>
+        <v>0.01293945</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>1570.082</v>
+        <v>1540.62</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>0.0286753</v>
+        <v>0.02488237</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>0.1235352</v>
+        <v>0.1016846</v>
       </c>
       <c r="W25" s="2" t="n">
-        <v>23.7352</v>
+        <v>23.48755</v>
       </c>
       <c r="X25" s="2" t="n">
-        <v>0.01390105</v>
+        <v>0.008073735</v>
       </c>
       <c r="Y25" s="2" t="n">
-        <v>1496.666</v>
+        <v>1497.989</v>
       </c>
       <c r="Z25" s="2" t="n">
-        <v>0.0006920407</v>
+        <v>0.001009231</v>
       </c>
       <c r="AA25" s="2" t="n">
-        <v>6.819954</v>
+        <v>6.897338</v>
       </c>
       <c r="AB25" s="2" t="n">
-        <v>7.056820000000001e-05</v>
+        <v>6.460313e-05</v>
       </c>
       <c r="AC25" s="2" t="n">
         <v>100</v>
@@ -3612,7 +3612,7 @@
       <c r="AN25" s="2" t="inlineStr"/>
       <c r="AO25" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
@@ -3624,13 +3624,13 @@
         <v>2</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46254.52092953704</v>
+        <v>46254.50426260417</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>57.72888333333334</v>
+        <v>33.7285</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>100.36</v>
@@ -3666,40 +3666,40 @@
         <v>87.75383918143945</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>999.7532</v>
+        <v>999.0445999999999</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>0.006247028</v>
+        <v>0.03992499</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>0.02679443</v>
+        <v>0.1965332</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>1570.002</v>
+        <v>1572.356</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>0.02168832</v>
+        <v>0.1521285</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>0.0994873</v>
+        <v>0.6082764000000001</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>23.69327</v>
+        <v>24.34576</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>0.007533138</v>
+        <v>0.0293769</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>1496.664</v>
+        <v>1496.648</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>0.0006807474</v>
+        <v>0.01245824</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>6.820149</v>
+        <v>6.814262</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>5.427905e-05</v>
+        <v>0.0003936504</v>
       </c>
       <c r="AC26" s="2" t="n">
         <v>100</v>
@@ -3724,9 +3724,13 @@
       </c>
       <c r="AJ26" s="2" t="inlineStr"/>
       <c r="AK26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AL26" s="2" t="inlineStr">
+        <is>
+          <t>+40.1 g IPA</t>
+        </is>
+      </c>
       <c r="AM26" s="2" t="b">
         <v>1</v>
       </c>
@@ -3745,13 +3749,13 @@
         <v>2</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46254.52231844908</v>
+        <v>46254.50426260417</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>59.72891666666667</v>
+        <v>33.7285</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>100.36</v>
@@ -3787,40 +3791,40 @@
         <v>87.75383918143945</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>999.7723</v>
+        <v>999.0445999999999</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>0.00495548</v>
+        <v>0.03992499</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>0.01947021</v>
+        <v>0.1965332</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>1569.93</v>
+        <v>1572.356</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>0.0206334</v>
+        <v>0.1521285</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>0.09436035</v>
+        <v>0.6082764000000001</v>
       </c>
       <c r="W27" s="2" t="n">
-        <v>23.66834</v>
+        <v>24.34576</v>
       </c>
       <c r="X27" s="2" t="n">
-        <v>0.007561989</v>
+        <v>0.0293769</v>
       </c>
       <c r="Y27" s="2" t="n">
-        <v>1496.664</v>
+        <v>1496.648</v>
       </c>
       <c r="Z27" s="2" t="n">
-        <v>0.00101814</v>
+        <v>0.01245824</v>
       </c>
       <c r="AA27" s="2" t="n">
-        <v>6.820327</v>
+        <v>6.814262</v>
       </c>
       <c r="AB27" s="2" t="n">
-        <v>5.14959e-05</v>
+        <v>0.0003936504</v>
       </c>
       <c r="AC27" s="2" t="n">
         <v>100</v>
@@ -3854,7 +3858,7 @@
       <c r="AN27" s="2" t="inlineStr"/>
       <c r="AO27" s="2" t="inlineStr">
         <is>
-          <t>Kennfeld_v2 (6).csv</t>
+          <t>Kennfeld_v2 (7).csv</t>
         </is>
       </c>
     </row>
@@ -3866,13 +3870,13 @@
         <v>2</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>46254.52370736111</v>
+        <v>46254.50565151621</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>61.72895</v>
+        <v>35.72853333333333</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>100.36</v>
@@ -3908,40 +3912,40 @@
         <v>87.75383918143945</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>999.7943</v>
+        <v>999.0505000000001</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>0.00692005</v>
+        <v>0.04014613</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>0.02514648</v>
+        <v>0.1531982</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>1569.84</v>
+        <v>1571.906</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>0.02849143</v>
+        <v>0.1086098</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>0.1147461</v>
+        <v>0.4274902</v>
       </c>
       <c r="W28" s="2" t="n">
-        <v>23.63219</v>
+        <v>24.34135</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>0.01081243</v>
+        <v>0.01313539</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>1496.662</v>
+        <v>1496.635</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>0.0009888646999999999</v>
+        <v>0.009172156000000001</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>6.82055</v>
+        <v>6.815417</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>7.086881e-05</v>
+        <v>0.0002764152</v>
       </c>
       <c r="AC28" s="2" t="n">
         <v>100</v>
@@ -3979,8 +3983,5453 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>46254.50565151621</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>35.72853333333333</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>999.0505000000001</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0.04014613</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>0.1531982</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>1571.906</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>0.1086098</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>0.4274902</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>24.34135</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>0.01313539</v>
+      </c>
+      <c r="Y29" s="2" t="n">
+        <v>1496.635</v>
+      </c>
+      <c r="Z29" s="2" t="n">
+        <v>0.009172156000000001</v>
+      </c>
+      <c r="AA29" s="2" t="n">
+        <v>6.815417</v>
+      </c>
+      <c r="AB29" s="2" t="n">
+        <v>0.0002764152</v>
+      </c>
+      <c r="AC29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="2" t="inlineStr"/>
+      <c r="AK29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="2" t="inlineStr"/>
+      <c r="AM29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN29" s="2" t="inlineStr"/>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>46254.50704042824</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>37.72856666666667</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>999.053</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0.08086706</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>0.3322754</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>1571.665</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>0.1730756</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>1.010498</v>
+      </c>
+      <c r="W30" s="2" t="n">
+        <v>24.29788</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>0.008551191</v>
+      </c>
+      <c r="Y30" s="2" t="n">
+        <v>1496.625</v>
+      </c>
+      <c r="Z30" s="2" t="n">
+        <v>0.01765049</v>
+      </c>
+      <c r="AA30" s="2" t="n">
+        <v>6.816027</v>
+      </c>
+      <c r="AB30" s="2" t="n">
+        <v>0.000443982</v>
+      </c>
+      <c r="AC30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr"/>
+      <c r="AK30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="2" t="inlineStr"/>
+      <c r="AM30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN30" s="2" t="inlineStr"/>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>46254.50704042824</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>37.72856666666667</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>999.053</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0.08086706</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0.3322754</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>1571.665</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>0.1730756</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>1.010498</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>24.29788</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>0.008551191</v>
+      </c>
+      <c r="Y31" s="2" t="n">
+        <v>1496.625</v>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <v>0.01765049</v>
+      </c>
+      <c r="AA31" s="2" t="n">
+        <v>6.816027</v>
+      </c>
+      <c r="AB31" s="2" t="n">
+        <v>0.000443982</v>
+      </c>
+      <c r="AC31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="2" t="inlineStr"/>
+      <c r="AK31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="2" t="inlineStr"/>
+      <c r="AM31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN31" s="2" t="inlineStr"/>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>46254.50842932871</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>39.72858333333333</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>999.2921</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0.06010251</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0.2545776</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>1571.253</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0.08578891</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0.3741455</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>24.24398</v>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>0.0163429</v>
+      </c>
+      <c r="Y32" s="2" t="n">
+        <v>1496.669</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>0.01277461</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>6.817075</v>
+      </c>
+      <c r="AB32" s="2" t="n">
+        <v>0.0002167475</v>
+      </c>
+      <c r="AC32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="2" t="inlineStr"/>
+      <c r="AK32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="2" t="inlineStr"/>
+      <c r="AM32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN32" s="2" t="inlineStr"/>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>46254.50842932871</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>39.72858333333333</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>999.2921</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0.06010251</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>0.2545776</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>1571.253</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>0.08578891</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>0.3741455</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>24.24398</v>
+      </c>
+      <c r="X33" s="2" t="n">
+        <v>0.0163429</v>
+      </c>
+      <c r="Y33" s="2" t="n">
+        <v>1496.669</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>0.01277461</v>
+      </c>
+      <c r="AA33" s="2" t="n">
+        <v>6.817075</v>
+      </c>
+      <c r="AB33" s="2" t="n">
+        <v>0.0002167475</v>
+      </c>
+      <c r="AC33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="2" t="inlineStr"/>
+      <c r="AK33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="2" t="inlineStr"/>
+      <c r="AM33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN33" s="2" t="inlineStr"/>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>46254.50981824074</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>41.72861666666667</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>999.4417</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0.0439833</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>0.2298584</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>1570.984</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>0.06117566</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>0.2178955</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>24.16846</v>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>0.0183495</v>
+      </c>
+      <c r="Y34" s="2" t="n">
+        <v>1496.688</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>0.01092934</v>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>6.817746</v>
+      </c>
+      <c r="AB34" s="2" t="n">
+        <v>0.0001529526</v>
+      </c>
+      <c r="AC34" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="2" t="inlineStr"/>
+      <c r="AK34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="2" t="inlineStr"/>
+      <c r="AM34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>46254.50981824074</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>41.72861666666667</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>999.4417</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0.0439833</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>0.2298584</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>1570.984</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>0.06117566</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>0.2178955</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>24.16846</v>
+      </c>
+      <c r="X35" s="2" t="n">
+        <v>0.0183495</v>
+      </c>
+      <c r="Y35" s="2" t="n">
+        <v>1496.688</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>0.01092934</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>6.817746</v>
+      </c>
+      <c r="AB35" s="2" t="n">
+        <v>0.0001529526</v>
+      </c>
+      <c r="AC35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="2" t="inlineStr"/>
+      <c r="AK35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="2" t="inlineStr"/>
+      <c r="AM35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN35" s="2" t="inlineStr"/>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>46254.51120715278</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>43.72865</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>999.497</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0.0747264</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>0.3393555</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>1570.849</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>0.03224536</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>0.1621094</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>24.1036</v>
+      </c>
+      <c r="X36" s="2" t="n">
+        <v>0.01423024</v>
+      </c>
+      <c r="Y36" s="2" t="n">
+        <v>1496.687</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>0.01634002</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>6.818077</v>
+      </c>
+      <c r="AB36" s="2" t="n">
+        <v>7.983372e-05</v>
+      </c>
+      <c r="AC36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="2" t="inlineStr"/>
+      <c r="AK36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="2" t="inlineStr"/>
+      <c r="AM36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN36" s="2" t="inlineStr"/>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>46254.51120715278</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>43.72865</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>999.497</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0.0747264</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>0.3393555</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>1570.849</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>0.03224536</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>0.1621094</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>24.1036</v>
+      </c>
+      <c r="X37" s="2" t="n">
+        <v>0.01423024</v>
+      </c>
+      <c r="Y37" s="2" t="n">
+        <v>1496.687</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>0.01634002</v>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>6.818077</v>
+      </c>
+      <c r="AB37" s="2" t="n">
+        <v>7.983372e-05</v>
+      </c>
+      <c r="AC37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="2" t="inlineStr"/>
+      <c r="AK37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="2" t="inlineStr"/>
+      <c r="AM37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN37" s="2" t="inlineStr"/>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>46254.51259606481</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>45.72868333333334</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>999.5633</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>0.01306258</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>0.04284668</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>1570.704</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>0.0494593</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>0.2075195</v>
+      </c>
+      <c r="W38" s="2" t="n">
+        <v>24.03886</v>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>0.0207684</v>
+      </c>
+      <c r="Y38" s="2" t="n">
+        <v>1496.689</v>
+      </c>
+      <c r="Z38" s="2" t="n">
+        <v>0.00212438</v>
+      </c>
+      <c r="AA38" s="2" t="n">
+        <v>6.818432</v>
+      </c>
+      <c r="AB38" s="2" t="n">
+        <v>0.0001221448</v>
+      </c>
+      <c r="AC38" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="2" t="inlineStr"/>
+      <c r="AK38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="2" t="inlineStr"/>
+      <c r="AM38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN38" s="2" t="inlineStr"/>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>46254.51259606481</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>45.72868333333334</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>999.5633</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>0.01306258</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>0.04284668</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>1570.704</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>0.0494593</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>0.2075195</v>
+      </c>
+      <c r="W39" s="2" t="n">
+        <v>24.03886</v>
+      </c>
+      <c r="X39" s="2" t="n">
+        <v>0.0207684</v>
+      </c>
+      <c r="Y39" s="2" t="n">
+        <v>1496.689</v>
+      </c>
+      <c r="Z39" s="2" t="n">
+        <v>0.00212438</v>
+      </c>
+      <c r="AA39" s="2" t="n">
+        <v>6.818432</v>
+      </c>
+      <c r="AB39" s="2" t="n">
+        <v>0.0001221448</v>
+      </c>
+      <c r="AC39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="2" t="inlineStr"/>
+      <c r="AK39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="2" t="inlineStr"/>
+      <c r="AM39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN39" s="2" t="inlineStr"/>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>46254.51398497685</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>47.72871666666666</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>999.6129</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>0.009706391</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>0.03479004</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>1570.538</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>0.03119711</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>0.130127</v>
+      </c>
+      <c r="W40" s="2" t="n">
+        <v>23.94936</v>
+      </c>
+      <c r="X40" s="2" t="n">
+        <v>0.01781276</v>
+      </c>
+      <c r="Y40" s="2" t="n">
+        <v>1496.681</v>
+      </c>
+      <c r="Z40" s="2" t="n">
+        <v>0.0009501228</v>
+      </c>
+      <c r="AA40" s="2" t="n">
+        <v>6.818836</v>
+      </c>
+      <c r="AB40" s="2" t="n">
+        <v>7.606435999999999e-05</v>
+      </c>
+      <c r="AC40" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="2" t="inlineStr"/>
+      <c r="AK40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL40" s="2" t="inlineStr"/>
+      <c r="AM40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>46254.51398497685</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>47.72871666666666</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>999.6129</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>0.009706391</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>0.03479004</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>1570.538</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>0.03119711</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>0.130127</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>23.94936</v>
+      </c>
+      <c r="X41" s="2" t="n">
+        <v>0.01781276</v>
+      </c>
+      <c r="Y41" s="2" t="n">
+        <v>1496.681</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>0.0009501228</v>
+      </c>
+      <c r="AA41" s="2" t="n">
+        <v>6.818836</v>
+      </c>
+      <c r="AB41" s="2" t="n">
+        <v>7.606435999999999e-05</v>
+      </c>
+      <c r="AC41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="2" t="inlineStr"/>
+      <c r="AK41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="2" t="inlineStr"/>
+      <c r="AM41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN41" s="2" t="inlineStr"/>
+      <c r="AO41" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>46254.51537388889</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>49.72875000000001</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>999.6426</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>0.007244701</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>0.02783203</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>1570.443</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>0.02649933</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>0.09753418</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>23.89672</v>
+      </c>
+      <c r="X42" s="2" t="n">
+        <v>0.01020618</v>
+      </c>
+      <c r="Y42" s="2" t="n">
+        <v>1496.679</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>0.000754301</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>6.819066</v>
+      </c>
+      <c r="AB42" s="2" t="n">
+        <v>6.589015e-05</v>
+      </c>
+      <c r="AC42" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="2" t="inlineStr"/>
+      <c r="AK42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="2" t="inlineStr"/>
+      <c r="AM42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN42" s="2" t="inlineStr"/>
+      <c r="AO42" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>46254.51537388889</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>49.72875000000001</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>999.6426</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>0.007244701</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>0.02783203</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>1570.443</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>0.02649933</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>0.09753418</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>23.89672</v>
+      </c>
+      <c r="X43" s="2" t="n">
+        <v>0.01020618</v>
+      </c>
+      <c r="Y43" s="2" t="n">
+        <v>1496.679</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>0.000754301</v>
+      </c>
+      <c r="AA43" s="2" t="n">
+        <v>6.819066</v>
+      </c>
+      <c r="AB43" s="2" t="n">
+        <v>6.589015e-05</v>
+      </c>
+      <c r="AC43" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="2" t="inlineStr"/>
+      <c r="AK43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="2" t="inlineStr"/>
+      <c r="AM43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN43" s="2" t="inlineStr"/>
+      <c r="AO43" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>46254.51676280093</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>51.72878333333334</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>999.6674</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>0.007222514</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>0.02850342</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>1570.347</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>0.03095584</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>0.1275635</v>
+      </c>
+      <c r="W44" s="2" t="n">
+        <v>23.85612</v>
+      </c>
+      <c r="X44" s="2" t="n">
+        <v>0.01159485</v>
+      </c>
+      <c r="Y44" s="2" t="n">
+        <v>1496.677</v>
+      </c>
+      <c r="Z44" s="2" t="n">
+        <v>0.001201592</v>
+      </c>
+      <c r="AA44" s="2" t="n">
+        <v>6.819304</v>
+      </c>
+      <c r="AB44" s="2" t="n">
+        <v>7.697795e-05</v>
+      </c>
+      <c r="AC44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="2" t="inlineStr"/>
+      <c r="AK44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="2" t="inlineStr"/>
+      <c r="AM44" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN44" s="2" t="inlineStr"/>
+      <c r="AO44" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>46254.51676280093</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>51.72878333333334</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>999.6674</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>0.007222514</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>0.02850342</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>1570.347</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>0.03095584</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>0.1275635</v>
+      </c>
+      <c r="W45" s="2" t="n">
+        <v>23.85612</v>
+      </c>
+      <c r="X45" s="2" t="n">
+        <v>0.01159485</v>
+      </c>
+      <c r="Y45" s="2" t="n">
+        <v>1496.677</v>
+      </c>
+      <c r="Z45" s="2" t="n">
+        <v>0.001201592</v>
+      </c>
+      <c r="AA45" s="2" t="n">
+        <v>6.819304</v>
+      </c>
+      <c r="AB45" s="2" t="n">
+        <v>7.697795e-05</v>
+      </c>
+      <c r="AC45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="2" t="inlineStr"/>
+      <c r="AK45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="2" t="inlineStr"/>
+      <c r="AM45" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN45" s="2" t="inlineStr"/>
+      <c r="AO45" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>46254.51815171296</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>53.72881666666667</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>999.6983</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>0.007676615</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>0.03082275</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>1570.217</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>0.03773323</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>0.1420898</v>
+      </c>
+      <c r="W46" s="2" t="n">
+        <v>23.80157</v>
+      </c>
+      <c r="X46" s="2" t="n">
+        <v>0.01671878</v>
+      </c>
+      <c r="Y46" s="2" t="n">
+        <v>1496.672</v>
+      </c>
+      <c r="Z46" s="2" t="n">
+        <v>0.002357753</v>
+      </c>
+      <c r="AA46" s="2" t="n">
+        <v>6.819623</v>
+      </c>
+      <c r="AB46" s="2" t="n">
+        <v>9.30431e-05</v>
+      </c>
+      <c r="AC46" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="2" t="inlineStr"/>
+      <c r="AK46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="2" t="inlineStr"/>
+      <c r="AM46" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN46" s="2" t="inlineStr"/>
+      <c r="AO46" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>46254.51815171296</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>53.72881666666667</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>999.6983</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>0.007676615</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>0.03082275</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>1570.217</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>0.03773323</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>0.1420898</v>
+      </c>
+      <c r="W47" s="2" t="n">
+        <v>23.80157</v>
+      </c>
+      <c r="X47" s="2" t="n">
+        <v>0.01671878</v>
+      </c>
+      <c r="Y47" s="2" t="n">
+        <v>1496.672</v>
+      </c>
+      <c r="Z47" s="2" t="n">
+        <v>0.002357753</v>
+      </c>
+      <c r="AA47" s="2" t="n">
+        <v>6.819623</v>
+      </c>
+      <c r="AB47" s="2" t="n">
+        <v>9.30431e-05</v>
+      </c>
+      <c r="AC47" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="2" t="inlineStr"/>
+      <c r="AK47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="2" t="inlineStr"/>
+      <c r="AM47" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN47" s="2" t="inlineStr"/>
+      <c r="AO47" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>46254.519540625</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>55.72885</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>999.7319</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0.009771835</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>0.03417969</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>1570.082</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>0.0286753</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>0.1235352</v>
+      </c>
+      <c r="W48" s="2" t="n">
+        <v>23.7352</v>
+      </c>
+      <c r="X48" s="2" t="n">
+        <v>0.01390105</v>
+      </c>
+      <c r="Y48" s="2" t="n">
+        <v>1496.666</v>
+      </c>
+      <c r="Z48" s="2" t="n">
+        <v>0.0006920407</v>
+      </c>
+      <c r="AA48" s="2" t="n">
+        <v>6.819954</v>
+      </c>
+      <c r="AB48" s="2" t="n">
+        <v>7.056820000000001e-05</v>
+      </c>
+      <c r="AC48" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="2" t="inlineStr"/>
+      <c r="AK48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL48" s="2" t="inlineStr"/>
+      <c r="AM48" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN48" s="2" t="inlineStr"/>
+      <c r="AO48" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>46254.519540625</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>55.72885</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>999.7319</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0.009771835</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>0.03417969</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>1570.082</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>0.0286753</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>0.1235352</v>
+      </c>
+      <c r="W49" s="2" t="n">
+        <v>23.7352</v>
+      </c>
+      <c r="X49" s="2" t="n">
+        <v>0.01390105</v>
+      </c>
+      <c r="Y49" s="2" t="n">
+        <v>1496.666</v>
+      </c>
+      <c r="Z49" s="2" t="n">
+        <v>0.0006920407</v>
+      </c>
+      <c r="AA49" s="2" t="n">
+        <v>6.819954</v>
+      </c>
+      <c r="AB49" s="2" t="n">
+        <v>7.056820000000001e-05</v>
+      </c>
+      <c r="AC49" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="2" t="inlineStr"/>
+      <c r="AK49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="2" t="inlineStr"/>
+      <c r="AM49" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN49" s="2" t="inlineStr"/>
+      <c r="AO49" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>46254.52092953704</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>57.72888333333334</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>999.7532</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0.006247028</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>0.02679443</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>1570.002</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>0.02168832</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>0.0994873</v>
+      </c>
+      <c r="W50" s="2" t="n">
+        <v>23.69327</v>
+      </c>
+      <c r="X50" s="2" t="n">
+        <v>0.007533138</v>
+      </c>
+      <c r="Y50" s="2" t="n">
+        <v>1496.664</v>
+      </c>
+      <c r="Z50" s="2" t="n">
+        <v>0.0006807474</v>
+      </c>
+      <c r="AA50" s="2" t="n">
+        <v>6.820149</v>
+      </c>
+      <c r="AB50" s="2" t="n">
+        <v>5.427905e-05</v>
+      </c>
+      <c r="AC50" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="2" t="inlineStr"/>
+      <c r="AK50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="2" t="inlineStr"/>
+      <c r="AM50" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN50" s="2" t="inlineStr"/>
+      <c r="AO50" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>46254.52092953704</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>57.72888333333334</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>999.7532</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0.006247028</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>0.02679443</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>1570.002</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>0.02168832</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>0.0994873</v>
+      </c>
+      <c r="W51" s="2" t="n">
+        <v>23.69327</v>
+      </c>
+      <c r="X51" s="2" t="n">
+        <v>0.007533138</v>
+      </c>
+      <c r="Y51" s="2" t="n">
+        <v>1496.664</v>
+      </c>
+      <c r="Z51" s="2" t="n">
+        <v>0.0006807474</v>
+      </c>
+      <c r="AA51" s="2" t="n">
+        <v>6.820149</v>
+      </c>
+      <c r="AB51" s="2" t="n">
+        <v>5.427905e-05</v>
+      </c>
+      <c r="AC51" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="2" t="inlineStr"/>
+      <c r="AK51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="2" t="inlineStr"/>
+      <c r="AM51" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN51" s="2" t="inlineStr"/>
+      <c r="AO51" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>46254.52231844908</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>59.72891666666667</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>999.7723</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0.00495548</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>0.01947021</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>1569.93</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>0.0206334</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>0.09436035</v>
+      </c>
+      <c r="W52" s="2" t="n">
+        <v>23.66834</v>
+      </c>
+      <c r="X52" s="2" t="n">
+        <v>0.007561989</v>
+      </c>
+      <c r="Y52" s="2" t="n">
+        <v>1496.664</v>
+      </c>
+      <c r="Z52" s="2" t="n">
+        <v>0.00101814</v>
+      </c>
+      <c r="AA52" s="2" t="n">
+        <v>6.820327</v>
+      </c>
+      <c r="AB52" s="2" t="n">
+        <v>5.14959e-05</v>
+      </c>
+      <c r="AC52" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="2" t="inlineStr"/>
+      <c r="AK52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="2" t="inlineStr"/>
+      <c r="AM52" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN52" s="2" t="inlineStr"/>
+      <c r="AO52" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>46254.52231844908</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>59.72891666666667</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>999.7723</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0.00495548</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>0.01947021</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>1569.93</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>0.0206334</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>0.09436035</v>
+      </c>
+      <c r="W53" s="2" t="n">
+        <v>23.66834</v>
+      </c>
+      <c r="X53" s="2" t="n">
+        <v>0.007561989</v>
+      </c>
+      <c r="Y53" s="2" t="n">
+        <v>1496.664</v>
+      </c>
+      <c r="Z53" s="2" t="n">
+        <v>0.00101814</v>
+      </c>
+      <c r="AA53" s="2" t="n">
+        <v>6.820327</v>
+      </c>
+      <c r="AB53" s="2" t="n">
+        <v>5.14959e-05</v>
+      </c>
+      <c r="AC53" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="2" t="inlineStr"/>
+      <c r="AK53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="2" t="inlineStr"/>
+      <c r="AM53" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN53" s="2" t="inlineStr"/>
+      <c r="AO53" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>46254.52370736111</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>61.72895</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>999.7943</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0.00692005</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>0.02514648</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>1569.84</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>0.02849143</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>0.1147461</v>
+      </c>
+      <c r="W54" s="2" t="n">
+        <v>23.63219</v>
+      </c>
+      <c r="X54" s="2" t="n">
+        <v>0.01081243</v>
+      </c>
+      <c r="Y54" s="2" t="n">
+        <v>1496.662</v>
+      </c>
+      <c r="Z54" s="2" t="n">
+        <v>0.0009888646999999999</v>
+      </c>
+      <c r="AA54" s="2" t="n">
+        <v>6.82055</v>
+      </c>
+      <c r="AB54" s="2" t="n">
+        <v>7.086881e-05</v>
+      </c>
+      <c r="AC54" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="2" t="inlineStr"/>
+      <c r="AK54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="2" t="inlineStr"/>
+      <c r="AM54" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN54" s="2" t="inlineStr"/>
+      <c r="AO54" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (6).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>46254.52370736111</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>61.72895</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>999.7943</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0.00692005</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>0.02514648</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>1569.84</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>0.02849143</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>0.1147461</v>
+      </c>
+      <c r="W55" s="2" t="n">
+        <v>23.63219</v>
+      </c>
+      <c r="X55" s="2" t="n">
+        <v>0.01081243</v>
+      </c>
+      <c r="Y55" s="2" t="n">
+        <v>1496.662</v>
+      </c>
+      <c r="Z55" s="2" t="n">
+        <v>0.0009888646999999999</v>
+      </c>
+      <c r="AA55" s="2" t="n">
+        <v>6.82055</v>
+      </c>
+      <c r="AB55" s="2" t="n">
+        <v>7.086881e-05</v>
+      </c>
+      <c r="AC55" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="2" t="inlineStr"/>
+      <c r="AK55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="2" t="inlineStr"/>
+      <c r="AM55" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN55" s="2" t="inlineStr"/>
+      <c r="AO55" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>46254.52509627315</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>63.72898333333333</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>999.8218000000001</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0.005795586</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>0.02185059</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>1569.718</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>0.03243058</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>0.142334</v>
+      </c>
+      <c r="W56" s="2" t="n">
+        <v>23.5817</v>
+      </c>
+      <c r="X56" s="2" t="n">
+        <v>0.0111766</v>
+      </c>
+      <c r="Y56" s="2" t="n">
+        <v>1496.658</v>
+      </c>
+      <c r="Z56" s="2" t="n">
+        <v>0.0009195374</v>
+      </c>
+      <c r="AA56" s="2" t="n">
+        <v>6.820851</v>
+      </c>
+      <c r="AB56" s="2" t="n">
+        <v>8.087698e-05</v>
+      </c>
+      <c r="AC56" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" s="2" t="inlineStr"/>
+      <c r="AK56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL56" s="2" t="inlineStr"/>
+      <c r="AM56" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN56" s="2" t="inlineStr"/>
+      <c r="AO56" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>46254.52648518518</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>65.72901666666668</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>999.8414</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0.004286509</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>0.0166626</v>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>1569.636</v>
+      </c>
+      <c r="U57" s="2" t="n">
+        <v>0.02060358</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>0.08862304999999999</v>
+      </c>
+      <c r="W57" s="2" t="n">
+        <v>23.55308</v>
+      </c>
+      <c r="X57" s="2" t="n">
+        <v>0.004808293</v>
+      </c>
+      <c r="Y57" s="2" t="n">
+        <v>1496.657</v>
+      </c>
+      <c r="Z57" s="2" t="n">
+        <v>0.0005371023</v>
+      </c>
+      <c r="AA57" s="2" t="n">
+        <v>6.821056</v>
+      </c>
+      <c r="AB57" s="2" t="n">
+        <v>5.21467e-05</v>
+      </c>
+      <c r="AC57" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="2" t="inlineStr"/>
+      <c r="AK57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="2" t="inlineStr"/>
+      <c r="AM57" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN57" s="2" t="inlineStr"/>
+      <c r="AO57" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>46254.52787409722</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>67.72905</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>999.8548</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0.004230333</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>0.01507568</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>1569.584</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>0.01587295</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>0.0736084</v>
+      </c>
+      <c r="W58" s="2" t="n">
+        <v>23.5359</v>
+      </c>
+      <c r="X58" s="2" t="n">
+        <v>0.002980403</v>
+      </c>
+      <c r="Y58" s="2" t="n">
+        <v>1496.658</v>
+      </c>
+      <c r="Z58" s="2" t="n">
+        <v>0.0006875752</v>
+      </c>
+      <c r="AA58" s="2" t="n">
+        <v>6.821184</v>
+      </c>
+      <c r="AB58" s="2" t="n">
+        <v>4.044098e-05</v>
+      </c>
+      <c r="AC58" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="2" t="inlineStr"/>
+      <c r="AK58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="2" t="inlineStr"/>
+      <c r="AM58" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN58" s="2" t="inlineStr"/>
+      <c r="AO58" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>46254.52926300926</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>69.72908333333334</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>999.8683</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0.003168878</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>0.01544189</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>1569.543</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>0.01757186</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>0.08532715</v>
+      </c>
+      <c r="W59" s="2" t="n">
+        <v>23.52662</v>
+      </c>
+      <c r="X59" s="2" t="n">
+        <v>0.002112462</v>
+      </c>
+      <c r="Y59" s="2" t="n">
+        <v>1496.66</v>
+      </c>
+      <c r="Z59" s="2" t="n">
+        <v>0.0005494</v>
+      </c>
+      <c r="AA59" s="2" t="n">
+        <v>6.821287</v>
+      </c>
+      <c r="AB59" s="2" t="n">
+        <v>4.495537e-05</v>
+      </c>
+      <c r="AC59" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="2" t="inlineStr"/>
+      <c r="AK59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="2" t="inlineStr"/>
+      <c r="AM59" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN59" s="2" t="inlineStr"/>
+      <c r="AO59" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>46254.5306519213</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>71.72911666666667</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>999.8849</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0.006518508</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>0.02429199</v>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>1569.457</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>0.02954062</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>0.1210938</v>
+      </c>
+      <c r="W60" s="2" t="n">
+        <v>23.50247</v>
+      </c>
+      <c r="X60" s="2" t="n">
+        <v>0.00981019</v>
+      </c>
+      <c r="Y60" s="2" t="n">
+        <v>1496.657</v>
+      </c>
+      <c r="Z60" s="2" t="n">
+        <v>0.0009992180000000001</v>
+      </c>
+      <c r="AA60" s="2" t="n">
+        <v>6.821502</v>
+      </c>
+      <c r="AB60" s="2" t="n">
+        <v>7.385007e-05</v>
+      </c>
+      <c r="AC60" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="2" t="inlineStr"/>
+      <c r="AK60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="2" t="inlineStr"/>
+      <c r="AM60" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN60" s="2" t="inlineStr"/>
+      <c r="AO60" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>46254.53204083334</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>73.72915000000002</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>999.9072</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0.005573285</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>0.02160645</v>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>1569.363</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>0.0222388</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>0.09960938</v>
+      </c>
+      <c r="W61" s="2" t="n">
+        <v>23.46238</v>
+      </c>
+      <c r="X61" s="2" t="n">
+        <v>0.009793876</v>
+      </c>
+      <c r="Y61" s="2" t="n">
+        <v>1496.654</v>
+      </c>
+      <c r="Z61" s="2" t="n">
+        <v>0.0007916424</v>
+      </c>
+      <c r="AA61" s="2" t="n">
+        <v>6.821734</v>
+      </c>
+      <c r="AB61" s="2" t="n">
+        <v>5.515276e-05</v>
+      </c>
+      <c r="AC61" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="2" t="inlineStr"/>
+      <c r="AK61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="2" t="inlineStr"/>
+      <c r="AM61" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN61" s="2" t="inlineStr"/>
+      <c r="AO61" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>46254.53342974537</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>75.72918333333334</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>999.9246000000001</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0.004986864</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>0.02026367</v>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>1569.288</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>0.02017396</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>0.09277344</v>
+      </c>
+      <c r="W62" s="2" t="n">
+        <v>23.43185</v>
+      </c>
+      <c r="X62" s="2" t="n">
+        <v>0.004554083</v>
+      </c>
+      <c r="Y62" s="2" t="n">
+        <v>1496.653</v>
+      </c>
+      <c r="Z62" s="2" t="n">
+        <v>0.0007216763</v>
+      </c>
+      <c r="AA62" s="2" t="n">
+        <v>6.82192</v>
+      </c>
+      <c r="AB62" s="2" t="n">
+        <v>5.106805e-05</v>
+      </c>
+      <c r="AC62" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="2" t="inlineStr"/>
+      <c r="AK62" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="2" t="inlineStr"/>
+      <c r="AM62" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN62" s="2" t="inlineStr"/>
+      <c r="AO62" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>46254.5348186574</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>77.72921666666667</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>999.9367</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0.003897404</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>0.01739502</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>1569.235</v>
+      </c>
+      <c r="U63" s="2" t="n">
+        <v>0.01784813</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>0.07678223000000001</v>
+      </c>
+      <c r="W63" s="2" t="n">
+        <v>23.42257</v>
+      </c>
+      <c r="X63" s="2" t="n">
+        <v>0.001209742</v>
+      </c>
+      <c r="Y63" s="2" t="n">
+        <v>1496.655</v>
+      </c>
+      <c r="Z63" s="2" t="n">
+        <v>0.0008996136</v>
+      </c>
+      <c r="AA63" s="2" t="n">
+        <v>6.822054</v>
+      </c>
+      <c r="AB63" s="2" t="n">
+        <v>4.58449e-05</v>
+      </c>
+      <c r="AC63" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="2" t="inlineStr"/>
+      <c r="AK63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="2" t="inlineStr"/>
+      <c r="AM63" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN63" s="2" t="inlineStr"/>
+      <c r="AO63" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>46254.53620756944</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>79.72925000000001</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>999.9444</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0.004208553</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>0.02056885</v>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>1569.203</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>0.01578968</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>0.0814209</v>
+      </c>
+      <c r="W64" s="2" t="n">
+        <v>23.42268</v>
+      </c>
+      <c r="X64" s="2" t="n">
+        <v>0.0004485385</v>
+      </c>
+      <c r="Y64" s="2" t="n">
+        <v>1496.657</v>
+      </c>
+      <c r="Z64" s="2" t="n">
+        <v>0.0009609093</v>
+      </c>
+      <c r="AA64" s="2" t="n">
+        <v>6.822137</v>
+      </c>
+      <c r="AB64" s="2" t="n">
+        <v>4.07916e-05</v>
+      </c>
+      <c r="AC64" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="2" t="inlineStr"/>
+      <c r="AK64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="2" t="inlineStr"/>
+      <c r="AM64" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN64" s="2" t="inlineStr"/>
+      <c r="AO64" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>46254.53759649306</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>81.72930000000001</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>999.9578</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0.005170687</v>
+      </c>
+      <c r="S65" s="2" t="n">
+        <v>0.02026367</v>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>1569.136</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>0.02707226</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>0.1326904</v>
+      </c>
+      <c r="W65" s="2" t="n">
+        <v>23.40995</v>
+      </c>
+      <c r="X65" s="2" t="n">
+        <v>0.007647671</v>
+      </c>
+      <c r="Y65" s="2" t="n">
+        <v>1496.656</v>
+      </c>
+      <c r="Z65" s="2" t="n">
+        <v>0.0009568909</v>
+      </c>
+      <c r="AA65" s="2" t="n">
+        <v>6.822307</v>
+      </c>
+      <c r="AB65" s="2" t="n">
+        <v>6.806207e-05</v>
+      </c>
+      <c r="AC65" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="2" t="inlineStr"/>
+      <c r="AK65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="2" t="inlineStr"/>
+      <c r="AM65" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN65" s="2" t="inlineStr"/>
+      <c r="AO65" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>46254.53898539352</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>83.72931666666666</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>999.9822</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0.02468955</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>0.1763916</v>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>1569.047</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>0.02317691</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>0.1210938</v>
+      </c>
+      <c r="W66" s="2" t="n">
+        <v>23.37662</v>
+      </c>
+      <c r="X66" s="2" t="n">
+        <v>0.007808542</v>
+      </c>
+      <c r="Y66" s="2" t="n">
+        <v>1496.656</v>
+      </c>
+      <c r="Z66" s="2" t="n">
+        <v>0.006197628</v>
+      </c>
+      <c r="AA66" s="2" t="n">
+        <v>6.822529</v>
+      </c>
+      <c r="AB66" s="2" t="n">
+        <v>5.811934e-05</v>
+      </c>
+      <c r="AC66" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" s="2" t="inlineStr"/>
+      <c r="AK66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL66" s="2" t="inlineStr"/>
+      <c r="AM66" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN66" s="2" t="inlineStr"/>
+      <c r="AO66" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>46254.54037431713</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>85.72936666666668</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>999.9893</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0.003698215</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>0.0145874</v>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>1569.001</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>0.01524501</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>0.06188965</v>
+      </c>
+      <c r="W67" s="2" t="n">
+        <v>23.36062</v>
+      </c>
+      <c r="X67" s="2" t="n">
+        <v>0.001248304</v>
+      </c>
+      <c r="Y67" s="2" t="n">
+        <v>1496.655</v>
+      </c>
+      <c r="Z67" s="2" t="n">
+        <v>0.001011335</v>
+      </c>
+      <c r="AA67" s="2" t="n">
+        <v>6.822643</v>
+      </c>
+      <c r="AB67" s="2" t="n">
+        <v>3.925327e-05</v>
+      </c>
+      <c r="AC67" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" s="2" t="inlineStr"/>
+      <c r="AK67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL67" s="2" t="inlineStr"/>
+      <c r="AM67" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN67" s="2" t="inlineStr"/>
+      <c r="AO67" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>46254.54176322916</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>87.7294</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>0.00472393</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>0.019104</v>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>1568.945</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>0.02137921</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>0.08996582</v>
+      </c>
+      <c r="W68" s="2" t="n">
+        <v>23.35149</v>
+      </c>
+      <c r="X68" s="2" t="n">
+        <v>0.003842897</v>
+      </c>
+      <c r="Y68" s="2" t="n">
+        <v>1496.656</v>
+      </c>
+      <c r="Z68" s="2" t="n">
+        <v>0.0005711076</v>
+      </c>
+      <c r="AA68" s="2" t="n">
+        <v>6.822785</v>
+      </c>
+      <c r="AB68" s="2" t="n">
+        <v>5.438524e-05</v>
+      </c>
+      <c r="AC68" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="2" t="inlineStr"/>
+      <c r="AK68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="2" t="inlineStr"/>
+      <c r="AM68" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN68" s="2" t="inlineStr"/>
+      <c r="AO68" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>46254.5431521412</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>89.72943333333335</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>1000.003</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0.0545422</v>
+      </c>
+      <c r="S69" s="2" t="n">
+        <v>0.276062</v>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>1568.866</v>
+      </c>
+      <c r="U69" s="2" t="n">
+        <v>0.0236528</v>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>0.0970459</v>
+      </c>
+      <c r="W69" s="2" t="n">
+        <v>23.33087</v>
+      </c>
+      <c r="X69" s="2" t="n">
+        <v>0.005022744</v>
+      </c>
+      <c r="Y69" s="2" t="n">
+        <v>1496.652</v>
+      </c>
+      <c r="Z69" s="2" t="n">
+        <v>0.01262699</v>
+      </c>
+      <c r="AA69" s="2" t="n">
+        <v>6.822983</v>
+      </c>
+      <c r="AB69" s="2" t="n">
+        <v>5.994344e-05</v>
+      </c>
+      <c r="AC69" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="2" t="inlineStr"/>
+      <c r="AK69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="2" t="inlineStr"/>
+      <c r="AM69" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN69" s="2" t="inlineStr"/>
+      <c r="AO69" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>46254.54454105324</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>91.72946666666667</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>1000.029</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>0.00361498</v>
+      </c>
+      <c r="S70" s="2" t="n">
+        <v>0.01507568</v>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>1568.816</v>
+      </c>
+      <c r="U70" s="2" t="n">
+        <v>0.0194244</v>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>0.08544922000000001</v>
+      </c>
+      <c r="W70" s="2" t="n">
+        <v>23.3174</v>
+      </c>
+      <c r="X70" s="2" t="n">
+        <v>0.003116159</v>
+      </c>
+      <c r="Y70" s="2" t="n">
+        <v>1496.656</v>
+      </c>
+      <c r="Z70" s="2" t="n">
+        <v>0.0005413466</v>
+      </c>
+      <c r="AA70" s="2" t="n">
+        <v>6.823109</v>
+      </c>
+      <c r="AB70" s="2" t="n">
+        <v>4.957198e-05</v>
+      </c>
+      <c r="AC70" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="2" t="inlineStr"/>
+      <c r="AK70" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="2" t="inlineStr"/>
+      <c r="AM70" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN70" s="2" t="inlineStr"/>
+      <c r="AO70" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>46254.54592996528</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>93.7295</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>1000.026</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>0.05325732</v>
+      </c>
+      <c r="S71" s="2" t="n">
+        <v>0.2702026</v>
+      </c>
+      <c r="T71" s="2" t="n">
+        <v>1568.737</v>
+      </c>
+      <c r="U71" s="2" t="n">
+        <v>0.02270034</v>
+      </c>
+      <c r="V71" s="2" t="n">
+        <v>0.1134033</v>
+      </c>
+      <c r="W71" s="2" t="n">
+        <v>23.30027</v>
+      </c>
+      <c r="X71" s="2" t="n">
+        <v>0.005608495</v>
+      </c>
+      <c r="Y71" s="2" t="n">
+        <v>1496.651</v>
+      </c>
+      <c r="Z71" s="2" t="n">
+        <v>0.0127115</v>
+      </c>
+      <c r="AA71" s="2" t="n">
+        <v>6.823307</v>
+      </c>
+      <c r="AB71" s="2" t="n">
+        <v>5.746847e-05</v>
+      </c>
+      <c r="AC71" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="2" t="inlineStr"/>
+      <c r="AK71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="2" t="inlineStr"/>
+      <c r="AM71" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN71" s="2" t="inlineStr"/>
+      <c r="AO71" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>46254.54731887732</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>95.72953333333334</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>1000.055</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>0.003963102</v>
+      </c>
+      <c r="S72" s="2" t="n">
+        <v>0.01654053</v>
+      </c>
+      <c r="T72" s="2" t="n">
+        <v>1568.671</v>
+      </c>
+      <c r="U72" s="2" t="n">
+        <v>0.01676338</v>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>0.07714844</v>
+      </c>
+      <c r="W72" s="2" t="n">
+        <v>23.28284</v>
+      </c>
+      <c r="X72" s="2" t="n">
+        <v>0.002213361</v>
+      </c>
+      <c r="Y72" s="2" t="n">
+        <v>1496.655</v>
+      </c>
+      <c r="Z72" s="2" t="n">
+        <v>0.0007739983</v>
+      </c>
+      <c r="AA72" s="2" t="n">
+        <v>6.823474</v>
+      </c>
+      <c r="AB72" s="2" t="n">
+        <v>4.291898e-05</v>
+      </c>
+      <c r="AC72" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" s="2" t="inlineStr"/>
+      <c r="AK72" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL72" s="2" t="inlineStr"/>
+      <c r="AM72" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN72" s="2" t="inlineStr"/>
+      <c r="AO72" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>46254.54870778935</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>97.72956666666667</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>1006.87</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>1147.38</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>1.749376841151144</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>6.998030295107114</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>3.498753682302289</v>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>87.75383918143945</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>1000.06</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>0.01939</v>
+      </c>
+      <c r="S73" s="2" t="n">
+        <v>0.09277344</v>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>1568.642</v>
+      </c>
+      <c r="U73" s="2" t="n">
+        <v>0.0156579</v>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>0.0748291</v>
+      </c>
+      <c r="W73" s="2" t="n">
+        <v>23.27919</v>
+      </c>
+      <c r="X73" s="2" t="n">
+        <v>0.001012985</v>
+      </c>
+      <c r="Y73" s="2" t="n">
+        <v>1496.656</v>
+      </c>
+      <c r="Z73" s="2" t="n">
+        <v>0.004574265</v>
+      </c>
+      <c r="AA73" s="2" t="n">
+        <v>6.823549</v>
+      </c>
+      <c r="AB73" s="2" t="n">
+        <v>4.030803e-05</v>
+      </c>
+      <c r="AC73" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="2" t="inlineStr"/>
+      <c r="AK73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="2" t="inlineStr"/>
+      <c r="AM73" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN73" s="2" t="inlineStr"/>
+      <c r="AO73" s="2" t="inlineStr">
+        <is>
+          <t>Kennfeld_v2 (7).csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO28"/>
+  <autoFilter ref="A1:AO73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4002,8 +9451,8 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
@@ -4096,7 +9545,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.6418166666666667</v>
@@ -4117,13 +9566,13 @@
         <v>997.0601</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.000699999999964364</v>
+        <v>0.0006260990336671595</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>1495.746666666667</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.006806859285457109</v>
+        <v>0.006088240030192224</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>24.64395333333333</v>
@@ -4143,7 +9592,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>7665671.645916668</v>
@@ -4164,13 +9613,13 @@
         <v>1004.938</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.002645751311141678</v>
+        <v>0.002366431913258192</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>1542.997</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.006000000000000227</v>
+        <v>0.005366563145984446</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>23.73179666666667</v>
@@ -4190,7 +9639,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>24.01633333333333</v>
@@ -4211,13 +9660,13 @@
         <v>837.8185</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>410.4455679247858</v>
+        <v>391.344493937944</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>1284.094</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>629.0750849261159</v>
+        <v>599.7995593035454</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>19.648165</v>
@@ -4237,10 +9686,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>61.72895</v>
+        <v>97.72956666666667</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1.749376841151144</v>
@@ -4255,22 +9704,22 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>999.5076733333333</v>
+        <v>999.6732625</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.2723019397304155</v>
+        <v>0.3047045570295364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1570.741066666666</v>
+        <v>1570.148333333333</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.7636005375537235</v>
+        <v>0.9938823581509416</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>23.984844</v>
+        <v>23.77070458333333</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>23.63219</v>
+        <v>23.27919</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>24.34576</v>
